--- a/src/test/resources/ImportTemplate/Validation - Flat File-SQL.xlsx
+++ b/src/test/resources/ImportTemplate/Validation - Flat File-SQL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD9D4D4-3712-4964-B682-56A023ECEC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAA17E3-8EED-466E-B659-6C5619507077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
     <t>|</t>
   </si>
   <si>
-    <t>R001_FlatFile-SQL_Validation</t>
+    <t>R00_FlatFile-SQL_Validation</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Validation - Flat File-SQL.xlsx
+++ b/src/test/resources/ImportTemplate/Validation - Flat File-SQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAA17E3-8EED-466E-B659-6C5619507077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CC813C-D2C3-4232-844E-E9A740E8CAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
     <t>|</t>
   </si>
   <si>
-    <t>R00_FlatFile-SQL_Validation</t>
+    <t>Validation_ImportSQL--File-FlatFile-SQL_Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Validation - Flat File-SQL.xlsx
+++ b/src/test/resources/ImportTemplate/Validation - Flat File-SQL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CC813C-D2C3-4232-844E-E9A740E8CAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA7C8DE-7377-4017-AF85-88F892F72E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
     <t>|</t>
   </si>
   <si>
-    <t>Validation_ImportSQL--File-FlatFile-SQL_Customer</t>
+    <t>Validation_ImportSQL__File_FlatFile_SQL_Customer</t>
   </si>
 </sst>
 </file>
